--- a/etl/working/RR 2026-06-03.xlsx
+++ b/etl/working/RR 2026-06-03.xlsx
@@ -16,20 +16,16 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
-    <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
   </numFmts>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -40,7 +36,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -48,22 +44,13 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -433,37 +420,37 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Index</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Outlook</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>BUY TRADE</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>SELL TRADE</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Prev Close</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>RR Date</t>
         </is>
@@ -477,24 +464,24 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>30-YEAR U.S. TREASURY YIELD</t>
+          <t>30-Year U.S. Treasury Yield</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Bullish</t>
+          <t>BULLISH</t>
         </is>
       </c>
       <c r="D2" t="n">
         <v>4.9</v>
       </c>
       <c r="E2" t="n">
-        <v>5.14</v>
+        <v>5.19</v>
       </c>
       <c r="F2" t="n">
-        <v>4.97</v>
-      </c>
-      <c r="G2" s="2" t="n">
+        <v>4.99</v>
+      </c>
+      <c r="G2" s="1" t="n">
         <v>46175</v>
       </c>
     </row>
@@ -506,24 +493,24 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>10-YEAR U.S. TREASURY YIELD</t>
+          <t>10-Year U.S. Treasury Yield</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Bullish</t>
+          <t>BULLISH</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>4.39</v>
       </c>
       <c r="E3" t="n">
-        <v>4.65</v>
+        <v>4.67</v>
       </c>
       <c r="F3" t="n">
-        <v>4.46</v>
-      </c>
-      <c r="G3" s="2" t="n">
+        <v>4.47</v>
+      </c>
+      <c r="G3" s="1" t="n">
         <v>46175</v>
       </c>
     </row>
@@ -535,16 +522,16 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2-YEAR U.S. TREASURY YIELD</t>
+          <t>2-Year U.S. Treasury Yield</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Bullish</t>
+          <t>BULLISH</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>3.97</v>
+        <v>3.95</v>
       </c>
       <c r="E4" t="n">
         <v>4.15</v>
@@ -552,7 +539,7 @@
       <c r="F4" t="n">
         <v>4.05</v>
       </c>
-      <c r="G4" s="2" t="n">
+      <c r="G4" s="1" t="n">
         <v>46175</v>
       </c>
     </row>
@@ -564,24 +551,24 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>HIGH YIELD</t>
+          <t>High Yield</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Bullish</t>
+          <t>BULLISH</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>79.33</v>
+        <v>79.15000000000001</v>
       </c>
       <c r="E5" t="n">
-        <v>80.18000000000001</v>
+        <v>80.2</v>
       </c>
       <c r="F5" t="n">
-        <v>79.90000000000001</v>
-      </c>
-      <c r="G5" s="2" t="n">
+        <v>79.84</v>
+      </c>
+      <c r="G5" s="1" t="n">
         <v>46175</v>
       </c>
     </row>
@@ -593,16 +580,16 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>INVESTMENT GRADE CORPORATE BOND ETF</t>
+          <t>Investment Grade Corporate Bond ETF</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>NEUTRAL</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>107.2</v>
+        <v>107</v>
       </c>
       <c r="E6" t="n">
         <v>109.6</v>
@@ -610,7 +597,7 @@
       <c r="F6" t="n">
         <v>108.9</v>
       </c>
-      <c r="G6" s="2" t="n">
+      <c r="G6" s="1" t="n">
         <v>46175</v>
       </c>
     </row>
@@ -627,19 +614,19 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Bullish</t>
+          <t>BULLISH</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>7398</v>
+        <v>7356</v>
       </c>
       <c r="E7" t="n">
-        <v>7661</v>
+        <v>7651</v>
       </c>
       <c r="F7" t="n">
-        <v>7610</v>
-      </c>
-      <c r="G7" s="2" t="n">
+        <v>7600</v>
+      </c>
+      <c r="G7" s="1" t="n">
         <v>46175</v>
       </c>
     </row>
@@ -651,24 +638,24 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>NASDAQ COMPOSITE</t>
+          <t>NASDAQ Composite</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Bullish</t>
+          <t>BULLISH</t>
         </is>
       </c>
       <c r="D8" t="n">
         <v>25940</v>
       </c>
       <c r="E8" t="n">
-        <v>27340</v>
+        <v>27327</v>
       </c>
       <c r="F8" t="n">
-        <v>27094</v>
-      </c>
-      <c r="G8" s="2" t="n">
+        <v>27087</v>
+      </c>
+      <c r="G8" s="1" t="n">
         <v>46175</v>
       </c>
     </row>
@@ -680,24 +667,24 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>RUSSELL 2000</t>
+          <t>Russell 2000</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Bullish</t>
+          <t>BULLISH</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>2829</v>
+        <v>2817</v>
       </c>
       <c r="E9" t="n">
-        <v>3011</v>
+        <v>2999</v>
       </c>
       <c r="F9" t="n">
-        <v>2932</v>
-      </c>
-      <c r="G9" s="2" t="n">
+        <v>2906</v>
+      </c>
+      <c r="G9" s="1" t="n">
         <v>46175</v>
       </c>
     </row>
@@ -709,24 +696,24 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>TECHNOLOGY SELECT SECTOR SPDR FUND</t>
+          <t>Technology Select Sector SPDR Fund</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Bullish</t>
+          <t>BULLISH</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="E10" t="n">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="F10" t="n">
-        <v>198</v>
-      </c>
-      <c r="G10" s="2" t="n">
+        <v>196</v>
+      </c>
+      <c r="G10" s="1" t="n">
         <v>46175</v>
       </c>
     </row>
@@ -738,24 +725,24 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>SPDR S&amp;P OIL &amp; GAS EXPLORE</t>
+          <t>SPDR S&amp;P Oil &amp; Gas Explore</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Bullish</t>
+          <t>BULLISH</t>
         </is>
       </c>
       <c r="D11" t="n">
         <v>161</v>
       </c>
       <c r="E11" t="n">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="F11" t="n">
-        <v>169</v>
-      </c>
-      <c r="G11" s="2" t="n">
+        <v>168</v>
+      </c>
+      <c r="G11" s="1" t="n">
         <v>46175</v>
       </c>
     </row>
@@ -767,24 +754,24 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>STATE STREET SPDR S&amp;P TELECOM ETF</t>
+          <t>State Street SPDR S&amp;P Telecom ETF</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Bullish</t>
+          <t>BULLISH</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="E12" t="n">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="F12" t="n">
-        <v>248</v>
-      </c>
-      <c r="G12" s="2" t="n">
+        <v>240</v>
+      </c>
+      <c r="G12" s="1" t="n">
         <v>46175</v>
       </c>
     </row>
@@ -796,24 +783,24 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>UTILITIES SELECT SECTOR SPDR FUND</t>
+          <t>Utilities Select Sector SPDR Fund</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Bearish</t>
+          <t>BEARISH</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>43.01</v>
+        <v>42.75</v>
       </c>
       <c r="E13" t="n">
         <v>45.12</v>
       </c>
       <c r="F13" t="n">
-        <v>43.9</v>
-      </c>
-      <c r="G13" s="2" t="n">
+        <v>43.1</v>
+      </c>
+      <c r="G13" s="1" t="n">
         <v>46175</v>
       </c>
     </row>
@@ -830,19 +817,19 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Bullish</t>
+          <t>BULLISH</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>4025</v>
+        <v>4014</v>
       </c>
       <c r="E14" t="n">
-        <v>4199</v>
+        <v>4189</v>
       </c>
       <c r="F14" t="n">
-        <v>4075</v>
-      </c>
-      <c r="G14" s="2" t="n">
+        <v>4056</v>
+      </c>
+      <c r="G14" s="1" t="n">
         <v>46175</v>
       </c>
     </row>
@@ -854,24 +841,24 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>NIKKEI 225 INDEX</t>
+          <t>Nikkei 225 Index</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Bullish</t>
+          <t>BULLISH</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>62283</v>
+        <v>62125</v>
       </c>
       <c r="E15" t="n">
-        <v>68439</v>
+        <v>68505</v>
       </c>
       <c r="F15" t="n">
-        <v>68402</v>
-      </c>
-      <c r="G15" s="2" t="n">
+        <v>66093</v>
+      </c>
+      <c r="G15" s="1" t="n">
         <v>46175</v>
       </c>
     </row>
@@ -883,24 +870,24 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>GERMAN DAX COMPOSITE</t>
+          <t>German DAX Composite</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Bullish</t>
+          <t>BULLISH</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>24519</v>
+        <v>24503</v>
       </c>
       <c r="E16" t="n">
-        <v>24995</v>
+        <v>25496</v>
       </c>
       <c r="F16" t="n">
-        <v>24934</v>
-      </c>
-      <c r="G16" s="2" t="n">
+        <v>25091</v>
+      </c>
+      <c r="G16" s="1" t="n">
         <v>46175</v>
       </c>
     </row>
@@ -912,24 +899,24 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>VOLATILITY INDEX</t>
+          <t>Volatility Index</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Bearish</t>
+          <t>BEARISH</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>14.92</v>
+        <v>14.9</v>
       </c>
       <c r="E17" t="n">
-        <v>17.84</v>
+        <v>17.98</v>
       </c>
       <c r="F17" t="n">
-        <v>15.77</v>
-      </c>
-      <c r="G17" s="2" t="n">
+        <v>16.05</v>
+      </c>
+      <c r="G17" s="1" t="n">
         <v>46175</v>
       </c>
     </row>
@@ -941,24 +928,24 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>U.S. DOLLAR INDEX</t>
+          <t>U.S. Dollar Index</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Bullish</t>
+          <t>BULLISH</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>98.77</v>
+        <v>98.76000000000001</v>
       </c>
       <c r="E18" t="n">
         <v>99.51000000000001</v>
       </c>
       <c r="F18" t="n">
-        <v>99.31</v>
-      </c>
-      <c r="G18" s="2" t="n">
+        <v>99.12</v>
+      </c>
+      <c r="G18" s="1" t="n">
         <v>46175</v>
       </c>
     </row>
@@ -970,24 +957,24 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>EURO TO U.S. DOLLAR</t>
+          <t>Euro to U.S. Dollar</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Bearish</t>
+          <t>BEARISH</t>
         </is>
       </c>
       <c r="D19" t="n">
         <v>1.157</v>
       </c>
       <c r="E19" t="n">
-        <v>1.166</v>
+        <v>1.167</v>
       </c>
       <c r="F19" t="n">
-        <v>1.162</v>
-      </c>
-      <c r="G19" s="2" t="n">
+        <v>1.164</v>
+      </c>
+      <c r="G19" s="1" t="n">
         <v>46175</v>
       </c>
     </row>
@@ -999,24 +986,24 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>U.S. DOLLAR TO JAPANESE YEN</t>
+          <t>U.S. Dollar to Japanese Yen</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Bullish</t>
+          <t>BULLISH</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>158.93</v>
+        <v>158.81</v>
       </c>
       <c r="E20" t="n">
-        <v>160.31</v>
+        <v>159.99</v>
       </c>
       <c r="F20" t="n">
-        <v>159.98</v>
-      </c>
-      <c r="G20" s="2" t="n">
+        <v>159.71</v>
+      </c>
+      <c r="G20" s="1" t="n">
         <v>46175</v>
       </c>
     </row>
@@ -1028,12 +1015,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>BRITISH POUND TO U.S. DOLLAR</t>
+          <t>British Pound to U.S. Dollar</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Bearish</t>
+          <t>BEARISH</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1043,9 +1030,9 @@
         <v>1.349</v>
       </c>
       <c r="F21" t="n">
-        <v>1.345</v>
-      </c>
-      <c r="G21" s="2" t="n">
+        <v>1.346</v>
+      </c>
+      <c r="G21" s="1" t="n">
         <v>46175</v>
       </c>
     </row>
@@ -1057,12 +1044,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>CANADIAN DOLLAR TO U.S. DOLLAR</t>
+          <t>Canadian Dollar to U.S. Dollar</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Bearish</t>
+          <t>BEARISH</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1074,7 +1061,7 @@
       <c r="F22" t="n">
         <v>0.722</v>
       </c>
-      <c r="G22" s="2" t="n">
+      <c r="G22" s="1" t="n">
         <v>46175</v>
       </c>
     </row>
@@ -1086,24 +1073,24 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>LIGHT CRUDE OIL CONTINUOUS CONTRACT</t>
+          <t>Light Crude Oil Continuous Contract</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Bullish</t>
+          <t>NEUTRAL</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>87.36</v>
+        <v>85.14</v>
       </c>
       <c r="E23" t="n">
-        <v>99.41</v>
+        <v>96.68000000000001</v>
       </c>
       <c r="F23" t="n">
-        <v>95.88</v>
-      </c>
-      <c r="G23" s="2" t="n">
+        <v>91.34999999999999</v>
+      </c>
+      <c r="G23" s="1" t="n">
         <v>46175</v>
       </c>
     </row>
@@ -1115,24 +1102,24 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>BRENT CRUDE OIL CONTINUOUS CONTRACT</t>
+          <t>Brent Crude Oil Continuous Contract</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Bullish</t>
+          <t>NEUTRAL</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="E24" t="n">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="F24" t="n">
-        <v>98</v>
-      </c>
-      <c r="G24" s="2" t="n">
+        <v>94</v>
+      </c>
+      <c r="G24" s="1" t="n">
         <v>46175</v>
       </c>
     </row>
@@ -1144,24 +1131,24 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>NATURAL GAS CONTINUOUS CONTRACT</t>
+          <t>Natural Gas Continuous Contract</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Bullish</t>
+          <t>BULLISH</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>2.98</v>
+        <v>2.95</v>
       </c>
       <c r="E25" t="n">
-        <v>3.41</v>
+        <v>3.46</v>
       </c>
       <c r="F25" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="G25" s="2" t="n">
+        <v>3.19</v>
+      </c>
+      <c r="G25" s="1" t="n">
         <v>46175</v>
       </c>
     </row>
@@ -1173,24 +1160,24 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>GOLD SPOT PRICE</t>
+          <t>Gold Spot Price</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>NEUTRAL</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>4421</v>
+        <v>4427</v>
       </c>
       <c r="E26" t="n">
-        <v>4573</v>
+        <v>4597</v>
       </c>
       <c r="F26" t="n">
-        <v>4486</v>
-      </c>
-      <c r="G26" s="2" t="n">
+        <v>4539</v>
+      </c>
+      <c r="G26" s="1" t="n">
         <v>46175</v>
       </c>
     </row>
@@ -1202,24 +1189,24 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>COPPER SPOT PRICE</t>
+          <t>Copper Spot Price</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Bullish</t>
+          <t>BULLISH</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>6.22</v>
+        <v>6.2</v>
       </c>
       <c r="E27" t="n">
-        <v>6.68</v>
+        <v>6.65</v>
       </c>
       <c r="F27" t="n">
-        <v>6.61</v>
-      </c>
-      <c r="G27" s="2" t="n">
+        <v>6.56</v>
+      </c>
+      <c r="G27" s="1" t="n">
         <v>46175</v>
       </c>
     </row>
@@ -1231,24 +1218,24 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>SILVER SPOT PRICE</t>
+          <t>Silver Spot Price</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Bearish</t>
+          <t>NEUTRAL</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E28" t="n">
         <v>78</v>
       </c>
       <c r="F28" t="n">
-        <v>74</v>
-      </c>
-      <c r="G28" s="2" t="n">
+        <v>76</v>
+      </c>
+      <c r="G28" s="1" t="n">
         <v>46175</v>
       </c>
     </row>
@@ -1260,24 +1247,24 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>MICROSOFT CORP.</t>
+          <t>Microsoft Corp.</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Bullish</t>
+          <t>BULLISH</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>412</v>
+        <v>419</v>
       </c>
       <c r="E29" t="n">
-        <v>460</v>
+        <v>466</v>
       </c>
       <c r="F29" t="n">
-        <v>441</v>
-      </c>
-      <c r="G29" s="2" t="n">
+        <v>461</v>
+      </c>
+      <c r="G29" s="1" t="n">
         <v>46175</v>
       </c>
     </row>
@@ -1289,24 +1276,24 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>APPLE INC.</t>
+          <t>Apple Inc.</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Bullish</t>
+          <t>BULLISH</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="E30" t="n">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="F30" t="n">
-        <v>315</v>
-      </c>
-      <c r="G30" s="2" t="n">
+        <v>306</v>
+      </c>
+      <c r="G30" s="1" t="n">
         <v>46175</v>
       </c>
     </row>
@@ -1318,24 +1305,24 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>AMAZON INC.</t>
+          <t>Amazon Inc.</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Bullish</t>
+          <t>BULLISH</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>251</v>
+        <v>258</v>
       </c>
       <c r="E31" t="n">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="F31" t="n">
-        <v>257</v>
-      </c>
-      <c r="G31" s="2" t="n">
+        <v>261</v>
+      </c>
+      <c r="G31" s="1" t="n">
         <v>46175</v>
       </c>
     </row>
@@ -1347,24 +1334,24 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>META PLATFORMS INC.</t>
+          <t>Meta Platforms Inc.</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Bearish</t>
+          <t>BEARISH</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="E32" t="n">
-        <v>635</v>
+        <v>630</v>
       </c>
       <c r="F32" t="n">
-        <v>598</v>
-      </c>
-      <c r="G32" s="2" t="n">
+        <v>600</v>
+      </c>
+      <c r="G32" s="1" t="n">
         <v>46175</v>
       </c>
     </row>
@@ -1376,24 +1363,24 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>ALPHABET INC.</t>
+          <t>Alphabet Inc.</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Bullish</t>
+          <t>BULLISH</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>358</v>
+        <v>372</v>
       </c>
       <c r="E33" t="n">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="F33" t="n">
-        <v>362</v>
-      </c>
-      <c r="G33" s="2" t="n">
+        <v>376</v>
+      </c>
+      <c r="G33" s="1" t="n">
         <v>46175</v>
       </c>
     </row>
@@ -1405,24 +1392,24 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>NETFLIX INC.</t>
+          <t>Netflix Inc.</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Bearish</t>
+          <t>BEARISH</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="E34" t="n">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="F34" t="n">
-        <v>83</v>
-      </c>
-      <c r="G34" s="2" t="n">
+        <v>86</v>
+      </c>
+      <c r="G34" s="1" t="n">
         <v>46175</v>
       </c>
     </row>
@@ -1434,24 +1421,24 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>TESLA INC.</t>
+          <t>Tesla Inc.</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Bullish</t>
+          <t>BULLISH</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>406</v>
+        <v>402</v>
       </c>
       <c r="E35" t="n">
         <v>445</v>
       </c>
       <c r="F35" t="n">
-        <v>424</v>
-      </c>
-      <c r="G35" s="2" t="n">
+        <v>416</v>
+      </c>
+      <c r="G35" s="1" t="n">
         <v>46175</v>
       </c>
     </row>
@@ -1463,24 +1450,24 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>NVIDIA CORPORATION</t>
+          <t>NVIDIA Corporation</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Bullish</t>
+          <t>BULLISH</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="E36" t="n">
         <v>230</v>
       </c>
       <c r="F36" t="n">
-        <v>223</v>
-      </c>
-      <c r="G36" s="2" t="n">
+        <v>224</v>
+      </c>
+      <c r="G36" s="1" t="n">
         <v>46175</v>
       </c>
     </row>
@@ -1492,24 +1479,24 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>ORACLE CORPORATION</t>
+          <t>Oracle Corporation</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Bullish</t>
+          <t>BULLISH</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>207</v>
+        <v>201</v>
       </c>
       <c r="E37" t="n">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="F37" t="n">
-        <v>245</v>
-      </c>
-      <c r="G37" s="2" t="n">
+        <v>248</v>
+      </c>
+      <c r="G37" s="1" t="n">
         <v>46175</v>
       </c>
     </row>
@@ -1521,24 +1508,24 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>BITCOIN SPOT PRICE</t>
+          <t>Bitcoin Spot Price</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Bearish</t>
+          <t>BEARISH</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>66004</v>
+        <v>69630</v>
       </c>
       <c r="E38" t="n">
-        <v>74003</v>
+        <v>75107</v>
       </c>
       <c r="F38" t="n">
-        <v>66840</v>
-      </c>
-      <c r="G38" s="2" t="n">
+        <v>70890</v>
+      </c>
+      <c r="G38" s="1" t="n">
         <v>46175</v>
       </c>
     </row>
@@ -1555,7 +1542,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Bullish</t>
+          <t>BULLISH</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1567,7 +1554,7 @@
       <c r="F39" t="n">
         <v>0</v>
       </c>
-      <c r="G39" s="2" t="n">
+      <c r="G39" s="1" t="n">
         <v>46175</v>
       </c>
     </row>
@@ -1584,7 +1571,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Bullish</t>
+          <t>BULLISH</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1596,7 +1583,7 @@
       <c r="F40" t="n">
         <v>0</v>
       </c>
-      <c r="G40" s="2" t="n">
+      <c r="G40" s="1" t="n">
         <v>46175</v>
       </c>
     </row>
@@ -1613,7 +1600,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Bullish</t>
+          <t>BULLISH</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1625,7 +1612,7 @@
       <c r="F41" t="n">
         <v>0</v>
       </c>
-      <c r="G41" s="2" t="n">
+      <c r="G41" s="1" t="n">
         <v>46175</v>
       </c>
     </row>
@@ -1642,7 +1629,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Bullish</t>
+          <t>BULLISH</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1654,7 +1641,7 @@
       <c r="F42" t="n">
         <v>0</v>
       </c>
-      <c r="G42" s="2" t="n">
+      <c r="G42" s="1" t="n">
         <v>46175</v>
       </c>
     </row>
@@ -1671,7 +1658,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Bullish</t>
+          <t>BULLISH</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1683,7 +1670,7 @@
       <c r="F43" t="n">
         <v>0</v>
       </c>
-      <c r="G43" s="2" t="n">
+      <c r="G43" s="1" t="n">
         <v>46175</v>
       </c>
     </row>
@@ -1700,7 +1687,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Bearish</t>
+          <t>BEARISH</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1712,7 +1699,7 @@
       <c r="F44" t="n">
         <v>0</v>
       </c>
-      <c r="G44" s="2" t="n">
+      <c r="G44" s="1" t="n">
         <v>46175</v>
       </c>
     </row>
@@ -1729,7 +1716,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Bullish</t>
+          <t>BEARISH</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1741,7 +1728,7 @@
       <c r="F45" t="n">
         <v>0</v>
       </c>
-      <c r="G45" s="2" t="n">
+      <c r="G45" s="1" t="n">
         <v>46175</v>
       </c>
     </row>
@@ -1758,7 +1745,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>NEUTRAL</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -1770,7 +1757,7 @@
       <c r="F46" t="n">
         <v>0</v>
       </c>
-      <c r="G46" s="2" t="n">
+      <c r="G46" s="1" t="n">
         <v>46175</v>
       </c>
     </row>
@@ -1787,7 +1774,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Bearish</t>
+          <t>BEARISH</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -1799,7 +1786,7 @@
       <c r="F47" t="n">
         <v>0</v>
       </c>
-      <c r="G47" s="2" t="n">
+      <c r="G47" s="1" t="n">
         <v>46175</v>
       </c>
     </row>
@@ -1816,7 +1803,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>BEARISH</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -1828,7 +1815,7 @@
       <c r="F48" t="n">
         <v>0</v>
       </c>
-      <c r="G48" s="2" t="n">
+      <c r="G48" s="1" t="n">
         <v>46175</v>
       </c>
     </row>
@@ -1845,7 +1832,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Bullish</t>
+          <t>BULLISH</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -1857,7 +1844,7 @@
       <c r="F49" t="n">
         <v>0</v>
       </c>
-      <c r="G49" s="2" t="n">
+      <c r="G49" s="1" t="n">
         <v>46175</v>
       </c>
     </row>
